--- a/Workforce_Capacity_and_Labor_Cost_Forecaster.xlsx
+++ b/Workforce_Capacity_and_Labor_Cost_Forecaster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anish\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{716D4ADA-A1F9-440C-BF87-BCBBF102BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D03C499-342F-466F-97ED-C3A27F27EB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{56AFA625-EC4C-4FEB-B91E-9B9D0212BCBA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{56AFA625-EC4C-4FEB-B91E-9B9D0212BCBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee_Master" sheetId="1" r:id="rId1"/>
@@ -343,7 +343,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$$-2809]#,##0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="171" formatCode="[$$-2809]#,##0.00"/>
     </dxf>
@@ -411,7 +414,7 @@
     <tableColumn id="2" xr3:uid="{A1E1A288-8EA8-413C-8B02-09326F87E8D3}" name=" Employee_Name"/>
     <tableColumn id="3" xr3:uid="{EA6C4062-8426-42C3-BD68-0969DC1B8514}" name=" Department"/>
     <tableColumn id="4" xr3:uid="{FCF0239C-2CDB-49B4-A0C9-8DC320837916}" name=" Role"/>
-    <tableColumn id="5" xr3:uid="{F8CCF282-961D-42F0-89CB-106B6154DA46}" name=" Hourly_Base_Rate"/>
+    <tableColumn id="5" xr3:uid="{F8CCF282-961D-42F0-89CB-106B6154DA46}" name=" Hourly_Base_Rate" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{DF4F85B1-89D4-40BA-816F-456E466655EB}" name=" Standard_Hours_Per_Day"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -423,7 +426,7 @@
   <autoFilter ref="A1:I7" xr:uid="{4E746639-1018-4036-975A-5F831B4D9B6B}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{05C63752-F0A7-43F8-AF7F-3DFE271DCD7A}" name="Log_ID "/>
-    <tableColumn id="2" xr3:uid="{A3FB4D54-C879-464D-B496-A18BEB56F6C7}" name=" Date " dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{A3FB4D54-C879-464D-B496-A18BEB56F6C7}" name=" Date " dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{DE968BD7-F285-4F87-8FA5-53DD9EEEF2B2}" name=" Employee_ID "/>
     <tableColumn id="4" xr3:uid="{01F3C9CA-ACE3-43DF-9795-3D4CC29DDCDE}" name=" Scheduled_Hours "/>
     <tableColumn id="5" xr3:uid="{1C850BB7-D5F2-423E-BA61-7DA8282A374D}" name=" Actual_Hours "/>
@@ -443,32 +446,32 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8DB8C840-694A-4F0F-8859-A44A73689F58}" name="Table2" displayName="Table2" ref="A1:I7" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8DB8C840-694A-4F0F-8859-A44A73689F58}" name="Table2" displayName="Table2" ref="A1:I7" totalsRowShown="0" headerRowDxfId="8" tableBorderDxfId="14">
   <autoFilter ref="A1:I7" xr:uid="{8DB8C840-694A-4F0F-8859-A44A73689F58}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{E0AA52D8-AF10-440F-A881-D4941CB8BBC1}" name="Employee_ID"/>
-    <tableColumn id="2" xr3:uid="{CD2E6042-7636-408F-A57B-E39F10193D8B}" name="Employee_Name" dataDxfId="5">
+    <tableColumn id="2" xr3:uid="{CD2E6042-7636-408F-A57B-E39F10193D8B}" name="Employee_Name" dataDxfId="6">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2, Employee_Master!$A$2:$A$7, Employee_Master!$B$2:$B$7, "Unknown")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DC1174F1-DD9F-481D-875D-12B5ABD15FA0}" name="Department" dataDxfId="4">
+    <tableColumn id="3" xr3:uid="{DC1174F1-DD9F-481D-875D-12B5ABD15FA0}" name="Department" dataDxfId="5">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2, Employee_Master!$A$2:$A$7, Employee_Master!$C$2:$C$7, "N/A")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{980107E6-13B6-4CEC-A454-1F21B37E1C17}" name="Hourly_Base_Rate" dataDxfId="3">
+    <tableColumn id="4" xr3:uid="{980107E6-13B6-4CEC-A454-1F21B37E1C17}" name="Hourly_Base_Rate" dataDxfId="4">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2, Employee_Master!$A$2:$A$7, Employee_Master!$E$2:$E$7, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{25FD6FD5-1938-4184-AE1F-73BE74AB74CF}" name="Total_Regular_Hours" dataDxfId="12">
+    <tableColumn id="5" xr3:uid="{25FD6FD5-1938-4184-AE1F-73BE74AB74CF}" name="Total_Regular_Hours" dataDxfId="13">
       <calculatedColumnFormula>SUMIF(Shift_Log_Engine!$C$2:$C$50, A2, Shift_Log_Engine!$G$2:$G$50)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{90330BD9-6D2E-44D4-9F8D-0FE9365AD4AA}" name="Total_OT_Hours" dataDxfId="11">
+    <tableColumn id="6" xr3:uid="{90330BD9-6D2E-44D4-9F8D-0FE9365AD4AA}" name="Total_OT_Hours" dataDxfId="12">
       <calculatedColumnFormula>SUMIF(Shift_Log_Engine!$C$2:$C$50, A2, Shift_Log_Engine!$H$2:$H$50)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{53836EC8-0A37-4B42-91E2-F2345D1E8855}" name="Regular_Payroll_Cost" dataDxfId="10">
+    <tableColumn id="7" xr3:uid="{53836EC8-0A37-4B42-91E2-F2345D1E8855}" name="Regular_Payroll_Cost" dataDxfId="11">
       <calculatedColumnFormula>E2 * D2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{0D4E2DF8-65BB-43DD-82F8-15F549C79CB0}" name="Overtime_Payroll_Cost" dataDxfId="9">
+    <tableColumn id="8" xr3:uid="{0D4E2DF8-65BB-43DD-82F8-15F549C79CB0}" name="Overtime_Payroll_Cost" dataDxfId="10">
       <calculatedColumnFormula>F2 * D2 * 1.5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{9E5535B2-3994-4997-AE81-DA7548BCA064}" name="Total_Payroll_Liability" dataDxfId="8">
+    <tableColumn id="9" xr3:uid="{9E5535B2-3994-4997-AE81-DA7548BCA064}" name="Total_Payroll_Liability" dataDxfId="9">
       <calculatedColumnFormula>G2 + H2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -481,13 +484,13 @@
   <autoFilter ref="A6:D9" xr:uid="{93284C1B-2462-4819-8B0A-B0389D7F9543}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{E80036D2-1456-4297-8218-2CF0ED19C5C0}" name="Department "/>
-    <tableColumn id="2" xr3:uid="{3E725441-A286-4880-A617-3628F9C57238}" name=" Regular Cost " dataDxfId="2">
+    <tableColumn id="2" xr3:uid="{3E725441-A286-4880-A617-3628F9C57238}" name=" Regular Cost " dataDxfId="3">
       <calculatedColumnFormula>SUMIF(Labor_Cost_Forecaster!$C$2:$C$7, A7, Labor_Cost_Forecaster!$G$2:$G$7)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4699F1F5-C573-482D-B566-65A40243463D}" name=" Overtime Cost " dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{4699F1F5-C573-482D-B566-65A40243463D}" name=" Overtime Cost " dataDxfId="2">
       <calculatedColumnFormula>SUMIF(Labor_Cost_Forecaster!$C$2:$C$7, A7, Labor_Cost_Forecaster!$H$2:$H$7)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F362CB46-42A8-495B-8D90-DCBAB1E7A157}" name=" Total Cost" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{F362CB46-42A8-495B-8D90-DCBAB1E7A157}" name=" Total Cost" dataDxfId="1">
       <calculatedColumnFormula>B7 + C7</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -856,7 +859,7 @@
       <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="8">
         <v>32.5</v>
       </c>
       <c r="F2">
@@ -876,7 +879,7 @@
       <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="8">
         <v>24</v>
       </c>
       <c r="F3">
@@ -896,7 +899,7 @@
       <c r="D4" t="s">
         <v>28</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="8">
         <v>21</v>
       </c>
       <c r="F4">
@@ -916,7 +919,7 @@
       <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="8">
         <v>38</v>
       </c>
       <c r="F5">
@@ -936,7 +939,7 @@
       <c r="D6" t="s">
         <v>34</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="8">
         <v>22.5</v>
       </c>
       <c r="F6">
@@ -956,7 +959,7 @@
       <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="8">
         <v>19.5</v>
       </c>
       <c r="F7">
